--- a/QUOTATION_EXCEL_TEMPLATES/ch_la_land/CH_LA_LAND_2026_QUOTATION.xlsx
+++ b/QUOTATION_EXCEL_TEMPLATES/ch_la_land/CH_LA_LAND_2026_QUOTATION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\다른 컴퓨터\내 컴퓨터\LK Group 관련\6. 중국-라오 육로 운송 과련\고객 견적 확인 요청건\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\QUOTATION_EXCEL_TEMPLATES\ch_la_land\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A04EB3C-D29D-494A-94DF-9F84D37039E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B76009-6794-43C5-8BF0-8DF4B898D2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="908" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="1005" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
@@ -851,10 +851,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>China-Lao Trucking 가견적</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>- 동 가견적 운임의 중량 및 크기는 단순 예상치이므로 최종 책정 방법인 기준인 실측시 금액 차이가 발생 할수 있으니, 참고용으로만 확인 부탁 드립니다.
 - 운임은 USD 기준이며, 이외 화폐는 가견적 안내시의 환율 기준이므로, 최종 운임 책정시의 환율변동으로 인한 운임 차이가 발생할수 있으니, 참고용으로만 확인 부탁 드립니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -866,6 +862,10 @@
   <si>
     <t>* 물품 출고 후 1주 후부터 보관료(최소 3불/CBM/day)가 발생하며, 특별한 사유 없이 2달 이상 보관 물품들은 임의로 폐기/처분 될 수 있습니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>China-Lao Trucking 가견적서</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1686,6 +1686,90 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="28" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1752,109 +1836,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="2" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="8" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1868,18 +1868,11 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1933,7 +1926,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$13:$F$33" spid="_x0000_s2067"/>
+                  <a14:cameraTool cellRange="$A$13:$F$33" spid="_x0000_s2068"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2147,8 +2140,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="50800" y="12623800"/>
-          <a:ext cx="7899400" cy="3733800"/>
+          <a:off x="50800" y="12782550"/>
+          <a:ext cx="7931150" cy="3727450"/>
           <a:chOff x="50800" y="15240000"/>
           <a:chExt cx="7899400" cy="3733800"/>
         </a:xfrm>
@@ -2279,8 +2272,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9931400" y="12598400"/>
-          <a:ext cx="7975600" cy="3719369"/>
+          <a:off x="9963150" y="12757150"/>
+          <a:ext cx="8020050" cy="3719369"/>
           <a:chOff x="9118600" y="15214600"/>
           <a:chExt cx="7975600" cy="3719369"/>
         </a:xfrm>
@@ -2417,8 +2410,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="19862800" y="12598399"/>
-          <a:ext cx="8026400" cy="3759201"/>
+          <a:off x="19945350" y="12757149"/>
+          <a:ext cx="8039100" cy="3752851"/>
           <a:chOff x="19761200" y="15214599"/>
           <a:chExt cx="8026400" cy="3747978"/>
         </a:xfrm>
@@ -2557,7 +2550,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$29" spid="_x0000_s1054"/>
+                  <a14:cameraTool cellRange="$A$1:$N$29" spid="_x0000_s1055"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2946,53 +2939,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:AD56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="4.09765625" style="36" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.3984375" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.125" style="36" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.375" style="36" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" style="36" customWidth="1"/>
-    <col min="7" max="7" width="6.09765625" style="36" customWidth="1"/>
+    <col min="7" max="7" width="6.125" style="36" customWidth="1"/>
     <col min="8" max="8" width="15" style="51" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.59765625" style="51" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.8984375" style="51" customWidth="1"/>
-    <col min="14" max="14" width="7.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.8984375" style="51" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.09765625" style="51" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.19921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.09765625" style="51" customWidth="1"/>
-    <col min="21" max="21" width="27.69921875" style="51" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" style="51" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.875" style="51" customWidth="1"/>
+    <col min="14" max="14" width="7.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.875" style="51" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.125" style="51" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.25" style="51" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.125" style="51" customWidth="1"/>
+    <col min="21" max="21" width="27.75" style="51" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22.5" style="51" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.69921875" style="51" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.75" style="51" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="38.5" style="51" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.19921875" style="51" customWidth="1"/>
+    <col min="26" max="26" width="4.25" style="51" customWidth="1"/>
     <col min="27" max="27" width="22" style="51" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.8984375" style="51" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.69921875" style="51" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.3984375" style="51" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.875" style="51" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.75" style="51" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.375" style="51" bestFit="1" customWidth="1"/>
     <col min="31" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:25">
-      <c r="B1" s="139" t="s">
+      <c r="B1" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="H1" s="142" t="s">
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="H1" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
     </row>
     <row r="2" spans="2:25">
       <c r="B2" s="37" t="s">
@@ -3056,30 +3049,30 @@
         <f>C4+D4</f>
         <v>34</v>
       </c>
-      <c r="H4" s="143" t="s">
+      <c r="H4" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="143" t="s">
+      <c r="I4" s="139"/>
+      <c r="J4" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="144"/>
-      <c r="N4" s="143" t="s">
+      <c r="K4" s="139"/>
+      <c r="N4" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="144"/>
-      <c r="P4" s="143" t="s">
+      <c r="O4" s="139"/>
+      <c r="P4" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="144"/>
-      <c r="U4" s="143" t="s">
+      <c r="Q4" s="139"/>
+      <c r="U4" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="139"/>
+      <c r="W4" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="144"/>
+      <c r="X4" s="139"/>
     </row>
     <row r="5" spans="2:25">
       <c r="B5" s="43" t="s">
@@ -3171,12 +3164,12 @@
       </c>
     </row>
     <row r="8" spans="2:25">
-      <c r="B8" s="141" t="s">
+      <c r="B8" s="143" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="141"/>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
       <c r="H8" s="37" t="s">
         <v>42</v>
       </c>
@@ -3221,12 +3214,12 @@
       </c>
     </row>
     <row r="9" spans="2:25">
-      <c r="B9" s="141" t="s">
+      <c r="B9" s="143" t="s">
         <v>223</v>
       </c>
-      <c r="C9" s="141"/>
-      <c r="D9" s="141"/>
-      <c r="E9" s="141"/>
+      <c r="C9" s="143"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="143"/>
       <c r="H9" s="37" t="s">
         <v>63</v>
       </c>
@@ -3704,11 +3697,11 @@
       </c>
       <c r="R21" s="61"/>
       <c r="S21" s="61"/>
-      <c r="U21" s="138" t="s">
+      <c r="U21" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="V21" s="138"/>
-      <c r="W21" s="138"/>
+      <c r="V21" s="141"/>
+      <c r="W21" s="141"/>
       <c r="X21" s="61">
         <f>SUM(X9:X20)</f>
         <v>0</v>
@@ -4091,11 +4084,11 @@
       </c>
       <c r="R32" s="61"/>
       <c r="S32" s="61"/>
-      <c r="U32" s="138" t="s">
+      <c r="U32" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="V32" s="138"/>
-      <c r="W32" s="138"/>
+      <c r="V32" s="141"/>
+      <c r="W32" s="141"/>
       <c r="X32" s="61">
         <f>SUM(X26:X31)</f>
         <v>0</v>
@@ -4188,12 +4181,12 @@
       </c>
       <c r="K36" s="61"/>
       <c r="L36" s="61"/>
-      <c r="N36" s="138" t="s">
+      <c r="N36" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="O36" s="138"/>
-      <c r="P36" s="138"/>
-      <c r="Q36" s="138"/>
+      <c r="O36" s="141"/>
+      <c r="P36" s="141"/>
+      <c r="Q36" s="141"/>
       <c r="R36" s="55">
         <f>SUM(R9:R35)</f>
         <v>0</v>
@@ -4355,11 +4348,11 @@
       <c r="O43" s="36"/>
       <c r="P43" s="36"/>
       <c r="Q43" s="36"/>
-      <c r="U43" s="138" t="s">
+      <c r="U43" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="V43" s="138"/>
-      <c r="W43" s="138"/>
+      <c r="V43" s="141"/>
+      <c r="W43" s="141"/>
       <c r="X43" s="61">
         <f>SUM(X37:X42)</f>
         <v>0</v>
@@ -4499,11 +4492,11 @@
       <c r="L55" s="55"/>
     </row>
     <row r="56" spans="8:12">
-      <c r="H56" s="138" t="s">
+      <c r="H56" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="I56" s="138"/>
-      <c r="J56" s="138"/>
+      <c r="I56" s="141"/>
+      <c r="J56" s="141"/>
       <c r="K56" s="58">
         <f>SUM(K9:K55)</f>
         <v>0</v>
@@ -4517,12 +4510,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="U35:X35"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="N36:Q36"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="U32:W32"/>
@@ -4537,6 +4524,12 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="N36:Q36"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4553,47 +4546,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="28.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.8984375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="39.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="39.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="48.19921875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="49.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="48.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="30.8984375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="30.875" style="1" customWidth="1"/>
     <col min="19" max="19" width="9" style="1"/>
-    <col min="20" max="23" width="36.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="36.375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="137" t="s">
-        <v>228</v>
-      </c>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
+      <c r="C1" s="102" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
       <c r="L1" s="80" t="s">
         <v>219</v>
       </c>
-      <c r="M1" s="124" t="s">
+      <c r="M1" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="N1" s="124"/>
+      <c r="N1" s="88"/>
       <c r="R1" s="24">
         <f>D11</f>
         <v>1</v>
@@ -4611,33 +4604,33 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="43.8">
+    <row r="2" spans="1:23" s="2" customFormat="1" ht="45">
       <c r="A2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="110"/>
+      <c r="C2" s="89"/>
       <c r="D2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="125" t="s">
+      <c r="E2" s="90" t="s">
         <v>227</v>
       </c>
-      <c r="F2" s="125"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="127" t="s">
+      <c r="F2" s="90"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="128"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="135" t="s">
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="100" t="s">
         <v>165</v>
       </c>
-      <c r="M2" s="136"/>
-      <c r="N2" s="133"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="98"/>
       <c r="R2" s="25">
         <f>N16</f>
         <v>0</v>
@@ -4657,25 +4650,25 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="2" customFormat="1" ht="43.8">
+    <row r="3" spans="1:23" s="2" customFormat="1" ht="45">
       <c r="A3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="134"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="101"/>
+      <c r="N3" s="99"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -4694,29 +4687,29 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="2" customFormat="1" ht="52.8">
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="54">
       <c r="A4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="111" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="114" t="s">
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="113" t="s">
         <v>207</v>
       </c>
-      <c r="M4" s="115"/>
-      <c r="N4" s="116"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="115"/>
       <c r="T4" s="34" t="s">
         <v>1</v>
       </c>
@@ -4732,7 +4725,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="5" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="23" t="s">
         <v>10</v>
       </c>
@@ -4751,11 +4744,11 @@
       <c r="F5" s="77" t="s">
         <v>182</v>
       </c>
-      <c r="G5" s="110" t="s">
+      <c r="G5" s="89" t="s">
         <v>218</v>
       </c>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
       <c r="J5" s="23" t="s">
         <v>183</v>
       </c>
@@ -4772,7 +4765,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="6" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="23">
         <v>1</v>
       </c>
@@ -4814,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="7" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="23">
         <v>2</v>
       </c>
@@ -4832,7 +4825,7 @@
       <c r="M7" s="22"/>
       <c r="N7" s="9"/>
     </row>
-    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="8" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="23">
         <v>3</v>
       </c>
@@ -4850,7 +4843,7 @@
       <c r="M8" s="22"/>
       <c r="N8" s="9"/>
     </row>
-    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="9" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="23">
         <v>4</v>
       </c>
@@ -4868,7 +4861,7 @@
       <c r="M9" s="22"/>
       <c r="N9" s="9"/>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
+    <row r="10" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="23">
         <v>5</v>
       </c>
@@ -4886,12 +4879,12 @@
       <c r="M10" s="22"/>
       <c r="N10" s="9"/>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A11" s="110" t="s">
+    <row r="11" spans="1:23" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A11" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="4">
         <f>SUM(D6:D10)</f>
         <v>1</v>
@@ -4914,44 +4907,44 @@
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="103" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="117"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="117" t="s">
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103" t="s">
         <v>190</v>
       </c>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="110" t="s">
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="120"/>
+      <c r="M12" s="106"/>
       <c r="N12" s="75">
         <f>SUM(N6:N11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A13" s="118" t="s">
-        <v>229</v>
-      </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
+    <row r="13" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A13" s="104" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="109"/>
       <c r="L13" s="81" t="s">
         <v>16</v>
       </c>
@@ -4964,18 +4957,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A14" s="117"/>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="123"/>
-      <c r="J14" s="123"/>
-      <c r="K14" s="123"/>
+    <row r="14" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A14" s="103"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="109"/>
       <c r="L14" s="81" t="s">
         <v>220</v>
       </c>
@@ -4988,18 +4981,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A15" s="117"/>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="123"/>
-      <c r="H15" s="123"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
+    <row r="15" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A15" s="103"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="109"/>
       <c r="L15" s="81" t="s">
         <v>221</v>
       </c>
@@ -5013,18 +5006,18 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A16" s="117"/>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="123"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="121" t="s">
+      <c r="A16" s="103"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="107" t="s">
         <v>192</v>
       </c>
       <c r="M16" s="72" t="s">
@@ -5036,18 +5029,18 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A17" s="117"/>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="123"/>
-      <c r="H17" s="123"/>
-      <c r="I17" s="123"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="122"/>
+      <c r="A17" s="103"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="109"/>
+      <c r="K17" s="109"/>
+      <c r="L17" s="108"/>
       <c r="M17" s="73" t="s">
         <v>18</v>
       </c>
@@ -5057,18 +5050,18 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A18" s="117"/>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="122"/>
+      <c r="A18" s="103"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="109"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="108"/>
       <c r="M18" s="74" t="s">
         <v>19</v>
       </c>
@@ -5077,19 +5070,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.95" customHeight="1">
-      <c r="A19" s="119"/>
-      <c r="B19" s="119"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="123"/>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="122"/>
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="52.9" customHeight="1">
+      <c r="A19" s="105"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="109"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="108"/>
       <c r="M19" s="15" t="s">
         <v>20</v>
       </c>
@@ -5114,165 +5107,165 @@
       <c r="M20" s="83"/>
       <c r="N20" s="83"/>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A21" s="90" t="s">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A21" s="118" t="s">
         <v>209</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A22" s="91" t="s">
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+    </row>
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A22" s="119" t="s">
         <v>222</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="91"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="91"/>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A23" s="107" t="s">
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
+    </row>
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A23" s="135" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" s="135"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="135"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="135"/>
+      <c r="N23" s="135"/>
+    </row>
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A24" s="119" t="s">
         <v>230</v>
       </c>
-      <c r="B23" s="107"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="107"/>
-      <c r="N23" s="107"/>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A24" s="91" t="s">
-        <v>231</v>
-      </c>
-      <c r="B24" s="91"/>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A25" s="92" t="s">
+      <c r="B24" s="119"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
+    </row>
+    <row r="25" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A25" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="93"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="100"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="128"/>
       <c r="F25" s="86"/>
       <c r="G25" s="16"/>
-      <c r="H25" s="108" t="s">
+      <c r="H25" s="136" t="s">
         <v>194</v>
       </c>
-      <c r="I25" s="108"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="88" t="s">
+      <c r="I25" s="136"/>
+      <c r="J25" s="137"/>
+      <c r="K25" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="L25" s="89"/>
-      <c r="M25" s="89"/>
-      <c r="N25" s="89"/>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A26" s="94"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="103"/>
+      <c r="L25" s="117"/>
+      <c r="M25" s="117"/>
+      <c r="N25" s="117"/>
+    </row>
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A26" s="122"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="130"/>
+      <c r="E26" s="131"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="H26" s="16"/>
       <c r="I26" s="16"/>
       <c r="J26" s="87"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="89"/>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A27" s="94"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="103"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="117"/>
+    </row>
+    <row r="27" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A27" s="122"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="131"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
       <c r="I27" s="16"/>
       <c r="J27" s="16"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="89"/>
-      <c r="M27" s="89"/>
-      <c r="N27" s="89"/>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A28" s="94"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="103"/>
+      <c r="K27" s="116"/>
+      <c r="L27" s="117"/>
+      <c r="M27" s="117"/>
+      <c r="N27" s="117"/>
+    </row>
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A28" s="122"/>
+      <c r="B28" s="123"/>
+      <c r="C28" s="129"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="131"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="I28" s="16"/>
       <c r="J28" s="16"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="89"/>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A29" s="96"/>
-      <c r="B29" s="97"/>
-      <c r="C29" s="104"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="106"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="117"/>
+    </row>
+    <row r="29" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A29" s="124"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="134"/>
       <c r="F29" s="27"/>
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="16"/>
       <c r="J29" s="16"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="89"/>
-    </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" ht="30">
+      <c r="K29" s="116"/>
+      <c r="L29" s="117"/>
+      <c r="M29" s="117"/>
+      <c r="N29" s="117"/>
+    </row>
+    <row r="30" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="17"/>
@@ -5288,7 +5281,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" ht="30">
+    <row r="31" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -5308,8 +5301,8 @@
     <row r="33" spans="17:22" ht="16.5" customHeight="1"/>
     <row r="34" spans="17:22" ht="16.5" customHeight="1"/>
     <row r="35" spans="17:22" ht="16.5" customHeight="1"/>
-    <row r="38" spans="17:22" ht="24.9" customHeight="1"/>
-    <row r="39" spans="17:22" ht="24.9" customHeight="1">
+    <row r="38" spans="17:22" ht="24.95" customHeight="1"/>
+    <row r="39" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q39" s="19"/>
       <c r="R39" s="19"/>
       <c r="S39" s="19"/>
@@ -5317,28 +5310,28 @@
       <c r="U39" s="19"/>
       <c r="V39" s="19"/>
     </row>
-    <row r="40" spans="17:22" ht="24.9" customHeight="1">
+    <row r="40" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q40" s="20"/>
     </row>
-    <row r="41" spans="17:22" ht="24.9" customHeight="1">
+    <row r="41" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q41" s="20"/>
     </row>
-    <row r="42" spans="17:22" ht="24.9" customHeight="1">
+    <row r="42" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q42" s="20"/>
     </row>
-    <row r="43" spans="17:22" ht="24.9" customHeight="1">
+    <row r="43" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q43" s="20"/>
     </row>
-    <row r="44" spans="17:22" ht="24.9" customHeight="1">
+    <row r="44" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q44" s="20"/>
     </row>
-    <row r="45" spans="17:22" ht="24.9" customHeight="1">
+    <row r="45" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q45" s="20"/>
     </row>
-    <row r="46" spans="17:22" ht="24.9" customHeight="1">
+    <row r="46" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q46" s="20"/>
     </row>
-    <row r="47" spans="17:22" ht="24.9" customHeight="1">
+    <row r="47" spans="17:22" ht="24.95" customHeight="1">
       <c r="Q47" s="20"/>
     </row>
     <row r="48" spans="17:22" ht="30" customHeight="1"/>
@@ -5359,25 +5352,6 @@
     <row r="63" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E19"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="L16:L19"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F13:K19"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:N4"/>
     <mergeCell ref="K25:K29"/>
     <mergeCell ref="L25:N29"/>
     <mergeCell ref="A21:N21"/>
@@ -5387,10 +5361,29 @@
     <mergeCell ref="A24:N24"/>
     <mergeCell ref="A23:N23"/>
     <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E19"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F13:K19"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C1:K1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="L6">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>N6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5400,7 +5393,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="27" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
